--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16254A36-0281-4F31-8229-9CD4E9014C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA88416-F0C0-4191-9FC0-6206F33A2369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -149,21 +149,6 @@
     <t>https://image.tmdb.org/t/p/original/uIWSyCt7StJlwzd8TMMtsIKrR9c.jpg</t>
   </si>
   <si>
-    <t>FastZone</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/6Zx9sabnYXtYHMg76JDTlpbBJFg.jpg</t>
-  </si>
-  <si>
-    <t>https://fdmjyllandsringen.dk/sites/jylland.dk/files/styles/image_1920x1080_xl/public/2025-12/Milj%C3%B8%20eller%20Banefaciliteter.jpg</t>
-  </si>
-  <si>
-    <t>RaceTV.dk</t>
-  </si>
-  <si>
-    <t>TV3 Sport</t>
-  </si>
-  <si>
     <t>Luksus til låns</t>
   </si>
   <si>
@@ -183,21 +168,6 @@
   </si>
   <si>
     <t>Kommissær Rex</t>
-  </si>
-  <si>
-    <t>Sport News</t>
-  </si>
-  <si>
-    <t>Viaplay Sport News</t>
-  </si>
-  <si>
-    <t>https://i-viaplay-com.akamaized.net/viaplay-prod/155/944/Sport_News1920x1080_SportNews_ok.jpg</t>
-  </si>
-  <si>
-    <t>TV-udbruddet</t>
-  </si>
-  <si>
-    <t>https://i-viaplay-com.akamaized.net/viaplay-prod/669/72/1757932138-001f38bb582cfdc1b238c8401d5f30fda461ee0e.jpg</t>
   </si>
 </sst>
 </file>
@@ -562,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -673,78 +643,34 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA88416-F0C0-4191-9FC0-6206F33A2369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EF00E1-C040-4904-964A-3CBAE240EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -168,6 +168,39 @@
   </si>
   <si>
     <t>Kommissær Rex</t>
+  </si>
+  <si>
+    <t>Christiania</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/eHyVk4Oli5QynMgUnYvPi2z8Dew.jpg</t>
+  </si>
+  <si>
+    <t>Der er et yndigt land</t>
+  </si>
+  <si>
+    <t>DR2</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/8wZYBHXBnnBPW8viE1LgMrVnqcZ.jpg</t>
+  </si>
+  <si>
+    <t>Døden i paradis</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/4pIpf4VRuiadvrkNe3YbdWMmPuO.jpg</t>
+  </si>
+  <si>
+    <t>Ægyptens forsvundne skatte</t>
+  </si>
+  <si>
+    <t>National Geographic</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/tC98UCxhJ4JOrA3vg6V7Yl5jRRg.jpg</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/dtVS1ZxmRr2F0N6XV8gcAlk3aom.jpg</t>
   </si>
 </sst>
 </file>
@@ -532,8 +565,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -541,7 +574,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -566,7 +599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -577,7 +610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -588,7 +621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -599,7 +632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -610,7 +643,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -621,7 +654,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -632,7 +665,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -643,34 +676,81 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -682,21 +762,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -704,7 +784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -712,7 +792,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -720,7 +800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -728,10 +808,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -739,7 +819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -747,7 +827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -755,7 +835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EF00E1-C040-4904-964A-3CBAE240EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63047FFE-9763-49BE-999F-6D2E717DADA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -201,6 +201,108 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/dtVS1ZxmRr2F0N6XV8gcAlk3aom.jpg</t>
+  </si>
+  <si>
+    <t>Shaolin</t>
+  </si>
+  <si>
+    <t>TV2</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/9JTs7Qxac9ezbwjMft99LxqeWkM.jpg</t>
+  </si>
+  <si>
+    <t>Dyrenes Danmark</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/mLL8By6Xk2P8TKp01pMxBheeBn1.jpg</t>
+  </si>
+  <si>
+    <t>Mennesket</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/3trar9jIi0sCjHvdXbNcWTWusAq.jpg</t>
+  </si>
+  <si>
+    <t>Robin Hood</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/frd6eaZjhRPseiA3cYutveTKKLI.jpg</t>
+  </si>
+  <si>
+    <t>Robinson Ekspeditionen</t>
+  </si>
+  <si>
+    <t>TV3 +</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/oruZ0uLDvqAa7WCFzar7rHyflc7.jpg</t>
+  </si>
+  <si>
+    <t>TV3 PULS</t>
+  </si>
+  <si>
+    <t>Masterchef - Danmarks største madtalenter</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/i4qIOWzZMAnhBg9xDkGhMN0kWg9.jpg</t>
+  </si>
+  <si>
+    <t>Bjerget</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/yjw0i6AEGkNpERwFOvdf0zUWIc.jpg</t>
+  </si>
+  <si>
+    <t>Gengangere</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/6rc15FSFb7CzV6PnaylPaN5xH3X.jpg</t>
+  </si>
+  <si>
+    <t>Sommerferie</t>
+  </si>
+  <si>
+    <t>https://is-cdn.tv2i.dk/epg/simplytv/20260804/e4fe4315-b025-4e90-a761-fed9c613b16c</t>
+  </si>
+  <si>
+    <t>Rick Stein elsker mad</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/6Pj0c1pMElBtwviGs1TjwEae7yU.jpg</t>
+  </si>
+  <si>
+    <t>Luksus i London</t>
+  </si>
+  <si>
+    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20260723/f80fce39-8d1d-4f11-b501-a3e4ebe82033</t>
+  </si>
+  <si>
+    <t>Sporten</t>
+  </si>
+  <si>
+    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20250401/f9601a8e-ce3a-4d14-be53-82731c1ed216</t>
+  </si>
+  <si>
+    <t>Tirsdagstrænerne</t>
+  </si>
+  <si>
+    <t>TV2 Sport X</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/q7hUNnbIlwMKWUFwKqjgOb1IOkQ.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold: A-Liga (k) - Kampe</t>
+  </si>
+  <si>
+    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20260711/5ef20ed5-e857-477c-ab0b-2d5c95df2b54</t>
+  </si>
+  <si>
+    <t>A-Liga: Målfesten</t>
+  </si>
+  <si>
+    <t>https://cdn-play.tv2i.dk/a171bad2-cad4-3158-aa01-eb8075e815d4.png</t>
   </si>
 </sst>
 </file>
@@ -565,8 +667,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -574,7 +676,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,7 +690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -599,7 +701,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -610,7 +712,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -621,7 +723,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -632,7 +734,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -643,7 +745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -654,7 +756,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -665,7 +767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -676,7 +778,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -687,7 +789,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -698,7 +800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -709,7 +811,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -720,7 +822,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -731,7 +833,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -742,7 +844,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -751,32 +853,198 @@
       </c>
       <c r="C16" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -784,7 +1052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -792,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -800,7 +1068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -808,10 +1076,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -819,7 +1087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -827,7 +1095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -835,7 +1103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63047FFE-9763-49BE-999F-6D2E717DADA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C4A6F2-1D77-4DD3-A560-83BA95DDB39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -303,6 +303,39 @@
   </si>
   <si>
     <t>https://cdn-play.tv2i.dk/a171bad2-cad4-3158-aa01-eb8075e815d4.png</t>
+  </si>
+  <si>
+    <t>Fear Factor</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/kOaK17y3RrfdfzNkQlRBdJPkYuK.jpg</t>
+  </si>
+  <si>
+    <t>Sportstalk</t>
+  </si>
+  <si>
+    <t>TV3</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/lPYoFaHcM12lvXSArkMEHZ1xiFk.jpg</t>
+  </si>
+  <si>
+    <t>PDC World Series of Darts</t>
+  </si>
+  <si>
+    <t>https://r2.thesportsdb.com/images/media/event/thumb/9ntkz41764591168.jpg</t>
+  </si>
+  <si>
+    <t>Little Giants</t>
+  </si>
+  <si>
+    <t>Animal Planet</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/ou18nyo1JjFTZ0h9lf4NEivuFWe.jpg</t>
+  </si>
+  <si>
+    <t>The Zoo</t>
   </si>
 </sst>
 </file>
@@ -667,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1018,6 +1051,58 @@
       </c>
       <c r="C31" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C4A6F2-1D77-4DD3-A560-83BA95DDB39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6959D6-F47E-4880-9348-46A116267CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>The Zoo</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/jnuGlgFOlSPUIBi6feF2iKkMyhz.jpg</t>
   </si>
 </sst>
 </file>
@@ -1104,6 +1107,9 @@
       <c r="B36" t="s">
         <v>101</v>
       </c>
+      <c r="C36" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6959D6-F47E-4880-9348-46A116267CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D5C14-4556-46C7-836C-CFE8C577741B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -339,6 +339,21 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/jnuGlgFOlSPUIBi6feF2iKkMyhz.jpg</t>
+  </si>
+  <si>
+    <t>Danskerklubben</t>
+  </si>
+  <si>
+    <t>Viaplay Sport News</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/s7MJ5BA4iA45uFWJAfpfJgvSOVr.jpg</t>
+  </si>
+  <si>
+    <t>Ansigt til ansigt</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/9xnUN1q5J34FL0HMCtOnQtkO2GY.jpg</t>
   </si>
 </sst>
 </file>
@@ -703,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1109,6 +1124,28 @@
       </c>
       <c r="C36" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D5C14-4556-46C7-836C-CFE8C577741B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B09FB9-6419-4046-B665-302161737F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="109">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -209,9 +209,6 @@
     <t>TV2</t>
   </si>
   <si>
-    <t>https://image.tmdb.org/t/p/original/9JTs7Qxac9ezbwjMft99LxqeWkM.jpg</t>
-  </si>
-  <si>
     <t>Dyrenes Danmark</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>Sommerferie</t>
   </si>
   <si>
-    <t>https://is-cdn.tv2i.dk/epg/simplytv/20260804/e4fe4315-b025-4e90-a761-fed9c613b16c</t>
-  </si>
-  <si>
     <t>Rick Stein elsker mad</t>
   </si>
   <si>
@@ -275,15 +269,9 @@
     <t>Luksus i London</t>
   </si>
   <si>
-    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20260723/f80fce39-8d1d-4f11-b501-a3e4ebe82033</t>
-  </si>
-  <si>
     <t>Sporten</t>
   </si>
   <si>
-    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20250401/f9601a8e-ce3a-4d14-be53-82731c1ed216</t>
-  </si>
-  <si>
     <t>Tirsdagstrænerne</t>
   </si>
   <si>
@@ -296,15 +284,9 @@
     <t>Fodbold: A-Liga (k) - Kampe</t>
   </si>
   <si>
-    <t>https://cmd-cdn.tv2i.dk/epg/whatson/20260711/5ef20ed5-e857-477c-ab0b-2d5c95df2b54</t>
-  </si>
-  <si>
     <t>A-Liga: Målfesten</t>
   </si>
   <si>
-    <t>https://cdn-play.tv2i.dk/a171bad2-cad4-3158-aa01-eb8075e815d4.png</t>
-  </si>
-  <si>
     <t>Fear Factor</t>
   </si>
   <si>
@@ -323,9 +305,6 @@
     <t>PDC World Series of Darts</t>
   </si>
   <si>
-    <t>https://r2.thesportsdb.com/images/media/event/thumb/9ntkz41764591168.jpg</t>
-  </si>
-  <si>
     <t>Little Giants</t>
   </si>
   <si>
@@ -354,13 +333,31 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/9xnUN1q5J34FL0HMCtOnQtkO2GY.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sporten.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +379,14 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -406,18 +411,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -743,415 +751,427 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
+        <v>83</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
+        <v>60</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
+        <v>60</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D38">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{47868A1E-1566-4B58-AC65-F13A3329546A}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
+    <hyperlink ref="C37" r:id="rId5" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
+    <hyperlink ref="C38" r:id="rId6" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B09FB9-6419-4046-B665-302161737F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F18924-337D-46BF-AC11-24D0FF4B5FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -338,19 +338,22 @@
     <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
   </si>
   <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sporten.jpg</t>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
+  </si>
+  <si>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Sporten.jpg</t>
+  </si>
+  <si>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
+  </si>
+  <si>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
+  </si>
+  <si>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Sommerferie.jpg</t>
+  </si>
+  <si>
+    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg</t>
   </si>
 </sst>
 </file>
@@ -757,7 +760,7 @@
         <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -768,7 +771,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -779,7 +782,7 @@
         <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -790,7 +793,7 @@
         <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1142,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1153,7 +1156,7 @@
         <v>90</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1163,12 +1166,12 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{47868A1E-1566-4B58-AC65-F13A3329546A}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
-    <hyperlink ref="C37" r:id="rId5" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
-    <hyperlink ref="C38" r:id="rId6" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sporten.jpg" xr:uid="{47868A1E-1566-4B58-AC65-F13A3329546A}"/>
+    <hyperlink ref="C4" r:id="rId3" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Luksus%20i%20London.jpg" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
+    <hyperlink ref="C37" r:id="rId5" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
+    <hyperlink ref="C38" r:id="rId6" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F18924-337D-46BF-AC11-24D0FF4B5FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB5BA9-1DBE-4A33-B75E-94F0D091E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,25 +335,25 @@
     <t>https://image.tmdb.org/t/p/original/9xnUN1q5J34FL0HMCtOnQtkO2GY.jpg</t>
   </si>
   <si>
-    <t>https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
-  </si>
-  <si>
-    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
-  </si>
-  <si>
-    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Sporten.jpg</t>
-  </si>
-  <si>
-    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
-  </si>
-  <si>
-    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
-  </si>
-  <si>
     <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Sommerferie.jpg</t>
   </si>
   <si>
     <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Sporten.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/9JTs7Qxac9ezbwjMft99LxqeWkM.jpg</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
         <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,7 +771,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -782,7 +782,7 @@
         <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -793,7 +793,7 @@
         <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,8 +891,8 @@
       <c r="B14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
-        <v>103</v>
+      <c r="C14" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1145,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>90</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1166,15 +1166,16 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
-    <hyperlink ref="C3" r:id="rId2" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sporten.jpg" xr:uid="{47868A1E-1566-4B58-AC65-F13A3329546A}"/>
-    <hyperlink ref="C4" r:id="rId3" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Luksus%20i%20London.jpg" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
-    <hyperlink ref="C37" r:id="rId5" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
-    <hyperlink ref="C38" r:id="rId6" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
+    <hyperlink ref="C37" r:id="rId4" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
+    <hyperlink ref="C38" r:id="rId5" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
+    <hyperlink ref="C3" r:id="rId6" xr:uid="{73720D26-DE20-4237-BB38-6063E44FFC54}"/>
+    <hyperlink ref="C14" r:id="rId7" xr:uid="{6C0F6182-15F9-48E4-8469-B90421228139}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB5BA9-1DBE-4A33-B75E-94F0D091E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D541B52F-4609-4704-8896-21454C93A216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -354,6 +354,36 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/9JTs7Qxac9ezbwjMft99LxqeWkM.jpg</t>
+  </si>
+  <si>
+    <t>Mexico Life</t>
+  </si>
+  <si>
+    <t>Kanal 4</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/vITrPPV6B25S0EEWebfouZf8YoL.jpg</t>
+  </si>
+  <si>
+    <t>Parterapi</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/6eE8VjzLYFJThVJSEY911L22dKe.jpg</t>
+  </si>
+  <si>
+    <t>Primal Instinct</t>
+  </si>
+  <si>
+    <t>Inv. Discovery</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/74kGVeUmiwWgNJg75IcDIJwhR6e.jpg</t>
+  </si>
+  <si>
+    <t>Let's be Frank</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/7Vc0Ycdw8J3zKzSi9tbnDy2lkIS.jpg</t>
   </si>
 </sst>
 </file>
@@ -729,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1157,6 +1187,50 @@
       </c>
       <c r="C38" s="4" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D541B52F-4609-4704-8896-21454C93A216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577E6921-BAAE-4940-B549-78F80CBDA02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1064,7 +1064,7 @@
       <c r="B27" t="s">
         <v>68</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1247,9 +1247,10 @@
     <hyperlink ref="C38" r:id="rId5" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
     <hyperlink ref="C3" r:id="rId6" xr:uid="{73720D26-DE20-4237-BB38-6063E44FFC54}"/>
     <hyperlink ref="C14" r:id="rId7" xr:uid="{6C0F6182-15F9-48E4-8469-B90421228139}"/>
+    <hyperlink ref="C27" r:id="rId8" xr:uid="{A5B69EBC-0B47-41D3-9652-D58814895521}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577E6921-BAAE-4940-B549-78F80CBDA02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC666BFE-E57D-484E-B355-BB500DE12BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -260,12 +260,6 @@
     <t>Sommerferie</t>
   </si>
   <si>
-    <t>Rick Stein elsker mad</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/6Pj0c1pMElBtwviGs1TjwEae7yU.jpg</t>
-  </si>
-  <si>
     <t>Luksus i London</t>
   </si>
   <si>
@@ -320,13 +314,7 @@
     <t>https://image.tmdb.org/t/p/original/jnuGlgFOlSPUIBi6feF2iKkMyhz.jpg</t>
   </si>
   <si>
-    <t>Danskerklubben</t>
-  </si>
-  <si>
     <t>Viaplay Sport News</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/s7MJ5BA4iA45uFWJAfpfJgvSOVr.jpg</t>
   </si>
   <si>
     <t>Ansigt til ansigt</t>
@@ -760,7 +748,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -768,7 +756,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,51 +770,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -837,7 +825,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -848,7 +836,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -859,7 +847,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -870,18 +858,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -892,7 +869,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -903,7 +880,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -914,7 +891,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -922,21 +899,21 @@
         <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -947,7 +924,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -958,7 +935,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -969,7 +946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -980,7 +957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -991,7 +968,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1002,29 +979,29 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
         <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1035,18 +1012,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
         <v>89</v>
       </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1057,7 +1034,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -1068,40 +1045,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
         <v>93</v>
       </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
         <v>82</v>
       </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -1112,7 +1078,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1123,7 +1089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1134,7 +1100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1145,7 +1111,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -1156,7 +1122,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1167,7 +1133,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1175,62 +1141,62 @@
         <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
       </c>
       <c r="C40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
         <v>115</v>
-      </c>
-      <c r="B41" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1257,21 +1223,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1279,7 +1245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1287,7 +1253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1295,7 +1261,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1303,10 +1269,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1314,7 +1280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1322,7 +1288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -1330,7 +1296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC666BFE-E57D-484E-B355-BB500DE12BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F91CE6-BEA4-4FE6-AA7F-874771831705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -248,9 +248,6 @@
     <t>Bjerget</t>
   </si>
   <si>
-    <t>https://image.tmdb.org/t/p/original/yjw0i6AEGkNpERwFOvdf0zUWIc.jpg</t>
-  </si>
-  <si>
     <t>Gengangere</t>
   </si>
   <si>
@@ -266,39 +263,12 @@
     <t>Sporten</t>
   </si>
   <si>
-    <t>Tirsdagstrænerne</t>
-  </si>
-  <si>
-    <t>TV2 Sport X</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/q7hUNnbIlwMKWUFwKqjgOb1IOkQ.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold: A-Liga (k) - Kampe</t>
-  </si>
-  <si>
-    <t>A-Liga: Målfesten</t>
-  </si>
-  <si>
     <t>Fear Factor</t>
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/kOaK17y3RrfdfzNkQlRBdJPkYuK.jpg</t>
   </si>
   <si>
-    <t>Sportstalk</t>
-  </si>
-  <si>
-    <t>TV3</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/lPYoFaHcM12lvXSArkMEHZ1xiFk.jpg</t>
-  </si>
-  <si>
-    <t>PDC World Series of Darts</t>
-  </si>
-  <si>
     <t>Little Giants</t>
   </si>
   <si>
@@ -314,9 +284,6 @@
     <t>https://image.tmdb.org/t/p/original/jnuGlgFOlSPUIBi6feF2iKkMyhz.jpg</t>
   </si>
   <si>
-    <t>Viaplay Sport News</t>
-  </si>
-  <si>
     <t>Ansigt til ansigt</t>
   </si>
   <si>
@@ -326,18 +293,9 @@
     <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/Sommerferie.jpg</t>
   </si>
   <si>
-    <t>raw.githubusercontent.com/flanaganz/epgoal/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/A-Liga%20M%C3%A5lfesten.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Sporten.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Fodbold%20A-Liga%20(k)%20-%20Kampe.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/flanaganz/epgoal/refs/heads/main/Manual_artwork_overrides/Luksus%20i%20London.jpg</t>
   </si>
   <si>
@@ -368,10 +326,13 @@
     <t>https://image.tmdb.org/t/p/original/74kGVeUmiwWgNJg75IcDIJwhR6e.jpg</t>
   </si>
   <si>
-    <t>Let's be Frank</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/7Vc0Ycdw8J3zKzSi9tbnDy2lkIS.jpg</t>
+    <t>Rovdyr</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/s7tOue9ljvRAy9CqqQ8U59RAuCJ.jpg</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/fuzWHBbSCtq99GUK3hInxEYTUOg.jpg</t>
   </si>
 </sst>
 </file>
@@ -747,8 +708,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -756,7 +717,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,51 +731,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -825,7 +778,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -836,7 +789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -847,7 +800,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -858,18 +811,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -880,7 +833,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -891,7 +844,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -899,21 +852,21 @@
         <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -924,7 +877,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -935,7 +888,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -946,7 +899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -957,7 +910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -968,7 +921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -979,29 +932,29 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1012,18 +965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1034,7 +976,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -1045,29 +987,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -1078,7 +1009,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1089,7 +1020,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1100,7 +1031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1111,7 +1042,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -1122,81 +1053,62 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
       </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C36" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1206,38 +1118,37 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{2926D03C-2247-489B-A570-DACF692E0B45}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{3D848CC7-0DEA-484D-A5B4-848E68221AC6}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
-    <hyperlink ref="C37" r:id="rId4" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
-    <hyperlink ref="C38" r:id="rId5" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/PDC%20World%20Series%20of%20Darts.jpg" xr:uid="{DDA077D7-F82D-47CF-85FE-95E22C07E86C}"/>
-    <hyperlink ref="C3" r:id="rId6" xr:uid="{73720D26-DE20-4237-BB38-6063E44FFC54}"/>
-    <hyperlink ref="C14" r:id="rId7" xr:uid="{6C0F6182-15F9-48E4-8469-B90421228139}"/>
-    <hyperlink ref="C27" r:id="rId8" xr:uid="{A5B69EBC-0B47-41D3-9652-D58814895521}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{6D9F4838-771D-49C6-8D14-315C5351741A}"/>
+    <hyperlink ref="C37" r:id="rId2" display="https://github.com/flanaganz/epgoal/blob/main/Manual_artwork_overrides/Sommerferie.jpg" xr:uid="{FAABBCF3-70C6-44F9-8D94-84F8D95F7D00}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{73720D26-DE20-4237-BB38-6063E44FFC54}"/>
+    <hyperlink ref="C14" r:id="rId4" xr:uid="{6C0F6182-15F9-48E4-8469-B90421228139}"/>
+    <hyperlink ref="C27" r:id="rId5" xr:uid="{A5B69EBC-0B47-41D3-9652-D58814895521}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{B7BD319E-7772-4897-A420-31A9B6641FBC}"/>
+    <hyperlink ref="C36" r:id="rId7" xr:uid="{B7FCDDA2-7488-402D-8FCB-D1E50E184830}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1245,7 +1156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1253,7 +1164,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1261,7 +1172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1269,10 +1180,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1280,7 +1191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1288,7 +1199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -1296,7 +1207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>

--- a/data/manual_artwork_overrides.xlsx
+++ b/data/manual_artwork_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F91CE6-BEA4-4FE6-AA7F-874771831705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0750140-4C2A-43EC-8676-FC4B89CFCA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manuelle overrides" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
   <si>
     <t>Titel (som i EPG)</t>
   </si>
@@ -333,6 +333,18 @@
   </si>
   <si>
     <t>https://image.tmdb.org/t/p/original/fuzWHBbSCtq99GUK3hInxEYTUOg.jpg</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/xpzD3tnKHdpKxujszTDKnYUjAli.jpg</t>
+  </si>
+  <si>
+    <t>Tuva &amp; Ronny - et lille hotel i Grækenland</t>
+  </si>
+  <si>
+    <t>Jorden Kalder</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/A5sHoMOAH3dpxK0zv3IoUDxRKn3.jpg</t>
   </si>
 </sst>
 </file>
@@ -754,7 +766,15 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="4"/>
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -809,6 +829,17 @@
       </c>
       <c r="C9" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1125,9 +1156,10 @@
     <hyperlink ref="C27" r:id="rId5" xr:uid="{A5B69EBC-0B47-41D3-9652-D58814895521}"/>
     <hyperlink ref="C2" r:id="rId6" xr:uid="{B7BD319E-7772-4897-A420-31A9B6641FBC}"/>
     <hyperlink ref="C36" r:id="rId7" xr:uid="{B7FCDDA2-7488-402D-8FCB-D1E50E184830}"/>
+    <hyperlink ref="C4" r:id="rId8" xr:uid="{8899D79B-99C3-4413-9749-AFADB8144293}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
